--- a/Codelist Excel Files and Conversion Templates to XML/verificationType.xlsx
+++ b/Codelist Excel Files and Conversion Templates to XML/verificationType.xlsx
@@ -1326,12 +1326,32 @@
         <f>IF(ISNA(VLOOKUP(B10,AssociatedElements!B$2:B2948,1,FALSE)),"Not used","")</f>
         <v/>
       </c>
-      <c r="B10" s="13" t="n"/>
-      <c r="C10" s="13" t="n"/>
-      <c r="D10" s="14" t="n"/>
-      <c r="E10" s="13" t="n"/>
+      <c r="B10" s="13" t="inlineStr">
+        <is>
+          <t>termination_criterion_trial_validation</t>
+        </is>
+      </c>
+      <c r="C10" s="13" t="inlineStr">
+        <is>
+          <t>Pre-production trial validation of termination criterion</t>
+        </is>
+      </c>
+      <c r="D10" s="14" t="inlineStr">
+        <is>
+          <t>Records the outcome of a pre-production indicator or trial column programme run to correlate drilling response against stratigraphy and confirm that the design's termination/refusal criterion is appropriate before production installation begins (V2 Installation row 43). Reuses diggs:DesignVerification's generic demand/capacity/outcome shape rather than a bespoke trial-programme object: the trial columns it draws on are already identifiable as diggs:RIColumn features whose samplingFeatureRef is absent (the schema's existing convention for a trial column), and this entry lets the correlation and validation performed against them be recorded as a verification like any other design check, with the specific columns and correlation reasoning carried in remark.</t>
+        </is>
+      </c>
+      <c r="E10" s="13" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
       <c r="F10" s="13" t="n"/>
-      <c r="G10" s="9" t="n"/>
+      <c r="G10" s="9" t="inlineStr">
+        <is>
+          <t>DIGGS</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="2">
@@ -1825,7 +1845,16 @@
         <f>IF(ISNA(VLOOKUP(B10,Definitions!B$2:B$1839,1,FALSE)),"Not listed","")</f>
         <v/>
       </c>
-      <c r="B10" s="20" t="n"/>
+      <c r="B10" s="20" t="inlineStr">
+        <is>
+          <t>termination_criterion_trial_validation</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>//diggs:DesignVerification/diggs:verificationType</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11">

--- a/Codelist Excel Files and Conversion Templates to XML/verificationType.xlsx
+++ b/Codelist Excel Files and Conversion Templates to XML/verificationType.xlsx
@@ -1338,7 +1338,7 @@
       </c>
       <c r="D10" s="14" t="inlineStr">
         <is>
-          <t>Records the outcome of a pre-production indicator or trial column programme run to correlate drilling response against stratigraphy and confirm that the design's termination/refusal criterion is appropriate before production installation begins (V2 Installation row 43). Reuses diggs:DesignVerification's generic demand/capacity/outcome shape rather than a bespoke trial-programme object: the trial columns it draws on are already identifiable as diggs:RIColumn features whose samplingFeatureRef is absent (the schema's existing convention for a trial column), and this entry lets the correlation and validation performed against them be recorded as a verification like any other design check, with the specific columns and correlation reasoning carried in remark.</t>
+          <t>Records the outcome of a pre-production indicator or trial column programme run to correlate drilling response against stratigraphy and confirm that the design's termination/refusal criterion is appropriate before production installation begins (V2 Installation row 43). Reuses diggs:DesignVerification's generic demand/capacity/outcome shape rather than a bespoke trial-programme object: the trial columns it draws on are already identifiable as diggs:RIColumn features whose mandatory elementClass is 'trial' (elementClass.xml, task EC1 - this superseded the earlier convention of an absent samplingFeatureRef, an element GR2 has since removed outright), and this entry lets the correlation and validation performed against them be recorded as a verification like any other design check, with the specific columns and correlation reasoning carried in remark.</t>
         </is>
       </c>
       <c r="E10" s="13" t="inlineStr">
@@ -1358,10 +1358,26 @@
         <f>IF(ISNA(VLOOKUP(B11,AssociatedElements!B$2:B2949,1,FALSE)),"Not used","")</f>
         <v/>
       </c>
-      <c r="B11" s="13" t="n"/>
-      <c r="C11" s="13" t="n"/>
-      <c r="D11" s="14" t="n"/>
-      <c r="E11" s="13" t="n"/>
+      <c r="B11" s="13" t="inlineStr">
+        <is>
+          <t>bending</t>
+        </is>
+      </c>
+      <c r="C11" s="13" t="inlineStr">
+        <is>
+          <t>Bending / flexural check</t>
+        </is>
+      </c>
+      <c r="D11" s="14" t="inlineStr">
+        <is>
+          <t>A structural check of the column's flexural capacity against the applied bending-moment demand. Distinct from the shear and structural_axial checks beside it: a rigid inclusion attracts moment wherever the ground moves laterally relative to it - alongside an embankment toe, across a liquefiable layer, or under a laterally loaded footing - and that demand is not derivable from the axial case. Carry the moment itself in demand/capacity, whose quantity class is then moment of force.</t>
+        </is>
+      </c>
+      <c r="E11" s="13" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
       <c r="F11" s="13" t="n"/>
       <c r="G11" s="9" t="n"/>
     </row>
@@ -1370,10 +1386,26 @@
         <f>IF(ISNA(VLOOKUP(B12,AssociatedElements!B$2:B2950,1,FALSE)),"Not used","")</f>
         <v/>
       </c>
-      <c r="B12" s="13" t="n"/>
-      <c r="C12" s="13" t="n"/>
-      <c r="D12" s="14" t="n"/>
-      <c r="E12" s="13" t="n"/>
+      <c r="B12" s="13" t="inlineStr">
+        <is>
+          <t>lateral</t>
+        </is>
+      </c>
+      <c r="C12" s="13" t="inlineStr">
+        <is>
+          <t>Lateral load check</t>
+        </is>
+      </c>
+      <c r="D12" s="14" t="inlineStr">
+        <is>
+          <t>A structural check of the column's lateral capacity against the applied lateral-force demand. Paired with bending, since the two are produced by the same load case and usually reported together, but kept separate because a section can satisfy one and fail the other. Distinct from lateral_spreading, which is a check on the GROUND mass moving, not on the column's capacity to resist a lateral force.</t>
+        </is>
+      </c>
+      <c r="E12" s="13" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
       <c r="F12" s="13" t="n"/>
       <c r="G12" s="9" t="n"/>
     </row>
@@ -1861,14 +1893,32 @@
         <f>IF(ISNA(VLOOKUP(B11,Definitions!B$2:B$1839,1,FALSE)),"Not listed","")</f>
         <v/>
       </c>
-      <c r="B11" s="20" t="n"/>
+      <c r="B11" s="20" t="inlineStr">
+        <is>
+          <t>bending</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>//diggs:DesignVerification/diggs:verificationType</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12">
         <f>IF(ISNA(VLOOKUP(B12,Definitions!B$2:B$1839,1,FALSE)),"Not listed","")</f>
         <v/>
       </c>
-      <c r="B12" s="20" t="n"/>
+      <c r="B12" s="20" t="inlineStr">
+        <is>
+          <t>lateral</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>//diggs:DesignVerification/diggs:verificationType</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13">
